--- a/Memphis_Grizzlies_2025-26_stats.xlsx
+++ b/Memphis_Grizzlies_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,35 +484,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Zach Edey</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PJ Hall</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cam Spencer</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Jock Landale</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>John Konchar</t>
         </is>
@@ -554,21 +559,24 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>10</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>14</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>10</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -605,24 +613,27 @@
         <v>12</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>7</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>8</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>16</v>
       </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
       <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -665,18 +676,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>27</v>
-      </c>
-      <c r="M4" t="n">
-        <v>8</v>
       </c>
       <c r="N4" t="n">
         <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -716,21 +730,24 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>9</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>11</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>17</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -773,18 +790,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>14</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -827,18 +847,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>13</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>12</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>16</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -878,21 +901,24 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>12</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>14</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -935,18 +961,21 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>17</v>
-      </c>
-      <c r="M9" t="n">
-        <v>13</v>
       </c>
       <c r="N9" t="n">
         <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -983,24 +1012,27 @@
         <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>19</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>11</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1043,18 +1075,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>21</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>12</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>11</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1097,18 +1132,21 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>13</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>10</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
       <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1151,18 +1189,21 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>11</v>
       </c>
       <c r="N13" t="n">
+        <v>11</v>
+      </c>
+      <c r="O13" t="n">
         <v>8</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1199,25 +1240,85 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>12</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>5</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>11</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>6</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,35 +1383,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Zach Edey</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PJ Hall</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cam Spencer</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Jock Landale</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>John Konchar</t>
         </is>
@@ -1355,18 +1461,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1406,21 +1515,24 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1463,18 +1575,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>4</v>
       </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1517,18 +1632,21 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1571,18 +1689,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
         <v>6</v>
       </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1625,18 +1746,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1679,18 +1803,21 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1733,18 +1860,21 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1781,24 +1911,27 @@
         <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1841,18 +1974,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1895,18 +2031,21 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>4</v>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1949,18 +2088,21 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>4</v>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1997,25 +2139,85 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
       <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2029,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,35 +2282,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Zach Edey</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PJ Hall</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cam Spencer</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Jock Landale</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>John Konchar</t>
         </is>
@@ -2150,21 +2357,24 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2201,24 +2411,27 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2258,21 +2471,24 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
         <v>8</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2309,24 +2525,27 @@
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2369,18 +2588,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2423,18 +2645,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>10</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2474,21 +2699,24 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2531,18 +2759,21 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>6</v>
       </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
       <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2579,24 +2810,27 @@
         <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>9</v>
       </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2639,18 +2873,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>9</v>
       </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
       <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2693,18 +2930,21 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
       <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
       <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2747,18 +2987,21 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
         <v>8</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2795,25 +3038,85 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>6</v>
       </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
       <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
         <v>6</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" t="n">
         <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2827,7 +3130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2878,35 +3181,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Zach Edey</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>PJ Hall</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cam Spencer</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Jock Landale</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>John Konchar</t>
         </is>
@@ -2954,15 +3262,18 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2999,16 +3310,16 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -3017,6 +3328,9 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3059,18 +3373,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>6</v>
       </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3113,18 +3430,21 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3167,18 +3487,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3224,15 +3547,18 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3278,15 +3604,18 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3329,18 +3658,21 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
         <v>4</v>
       </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3386,15 +3718,18 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3437,18 +3772,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3491,18 +3829,21 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3548,15 +3889,18 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3599,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -3608,9 +3952,69 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3625,7 +4029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,7 +4051,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.90909090909091</v>
+        <v>17.91666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -3657,7 +4061,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.23076923076923</v>
+        <v>17.85714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -3667,57 +4071,57 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.30769230769231</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Zach Edey</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.69230769230769</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.69230769230769</v>
+        <v>12.64285714285714</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jaylen Wells</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.615384615384615</v>
+        <v>10.28571428571429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Jaylen Wells</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.153846153846153</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kentavious Caldwell-Pope</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.076923076923077</v>
+        <v>8.714285714285714</v>
       </c>
     </row>
     <row r="10">
@@ -3733,50 +4137,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>Kentavious Caldwell-Pope</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.25</v>
+        <v>7.928571428571429</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Javon Small</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.636363636363636</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>GG Jackson</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>PJ Hall</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>1.857142857142857</v>
       </c>
     </row>
@@ -3791,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3813,7 +4227,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.090909090909092</v>
+        <v>7.583333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3823,7 +4237,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.076923076923077</v>
+        <v>3.071428571428572</v>
       </c>
     </row>
     <row r="4">
@@ -3833,7 +4247,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.076923076923077</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3859,21 +4273,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.538461538461538</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.375</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -3883,7 +4297,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.769230769230769</v>
+        <v>1.714285714285714</v>
       </c>
     </row>
     <row r="10">
@@ -3893,7 +4307,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.615384615384615</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -3903,7 +4317,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.307692307692308</v>
+        <v>1.357142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -3913,7 +4327,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="13">
@@ -3944,6 +4358,16 @@
       </c>
       <c r="B15" t="n">
         <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Zach Edey</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3957,7 +4381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3975,61 +4399,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Santi Aldama</t>
+          <t>Zach Edey</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.538461538461538</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Santi Aldama</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.923076923076923</v>
+        <v>6.857142857142857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.461538461538462</v>
+        <v>6.071428571428571</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jaren Jackson Jr.</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.230769230769231</v>
+        <v>5.428571428571429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Jaren Jackson Jr.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.25</v>
+        <v>5.214285714285714</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ja Morant</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.727272727272727</v>
+        <v>4.222222222222222</v>
       </c>
     </row>
     <row r="8">
@@ -4039,37 +4463,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.692307692307693</v>
+        <v>3.571428571428572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kentavious Caldwell-Pope</t>
+          <t>Ja Morant</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.769230769230769</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>John Konchar</t>
+          <t>Kentavious Caldwell-Pope</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.272727272727273</v>
+        <v>2.571428571428572</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>John Konchar</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.076923076923077</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -4085,30 +4509,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PJ Hall</t>
+          <t>Cam Spencer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.285714285714286</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Javon Small</t>
+          <t>PJ Hall</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>1.285714285714286</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Javon Small</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4123,7 +4557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4145,7 +4579,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.076923076923077</v>
+        <v>1.928571428571429</v>
       </c>
     </row>
     <row r="3">
@@ -4155,7 +4589,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.615384615384615</v>
+        <v>1.642857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -4165,23 +4599,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.615384615384615</v>
+        <v>1.642857142857143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jaylen Wells</t>
+          <t>Vince Williams Jr.</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.538461538461539</v>
+        <v>1.555555555555556</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vince Williams Jr.</t>
+          <t>Jaylen Wells</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4195,7 +4629,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.384615384615385</v>
+        <v>1.428571428571429</v>
       </c>
     </row>
     <row r="8">
@@ -4205,7 +4639,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.230769230769231</v>
+        <v>1.142857142857143</v>
       </c>
     </row>
     <row r="9">
@@ -4215,7 +4649,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.076923076923077</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4225,7 +4659,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -4245,7 +4679,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -4261,7 +4695,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Zach Edey</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -4271,10 +4705,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Olivier-Maxence Prosper</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4289,7 +4733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4592,6 +5036,27 @@
         <v>226</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>108</v>
+      </c>
+      <c r="E15" t="n">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
